--- a/data/trans_orig/P16A15-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A15-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>465657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>467489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>959686</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>961553</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>728747</t>
+          <t>728505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>619593</t>
+          <t>618852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1352024</t>
+          <t>1351866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360038</t>
+          <t>1359943</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24327</t>
+          <t>24030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23715</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19154</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40544</t>
+          <t>40405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613322</t>
+          <t>613619</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629174</t>
+          <t>628750</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>666029</t>
+          <t>667767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681891</t>
+          <t>682539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286850</t>
+          <t>1286989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1308240</t>
+          <t>1308232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20761</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40689</t>
+          <t>41105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34960</t>
+          <t>34878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41405</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68335</t>
+          <t>70345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478458</t>
+          <t>478042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>498810</t>
+          <t>498386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>480682</t>
+          <t>480764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>498915</t>
+          <t>499070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>966454</t>
+          <t>964444</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>993384</t>
+          <t>993037</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41216</t>
+          <t>41423</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67407</t>
+          <t>66783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>46925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76858</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96516</t>
+          <t>94606</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133833</t>
+          <t>132595</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319303</t>
+          <t>319927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>345494</t>
+          <t>345287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327128</t>
+          <t>326984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>356727</t>
+          <t>357061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>656863</t>
+          <t>658101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>694180</t>
+          <t>696090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39133</t>
+          <t>40208</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63375</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71731</t>
+          <t>69653</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100731</t>
+          <t>100949</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116215</t>
+          <t>115649</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>156495</t>
+          <t>158390</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229208</t>
+          <t>228300</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253450</t>
+          <t>252375</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242203</t>
+          <t>241985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271203</t>
+          <t>273281</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479022</t>
+          <t>477127</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519302</t>
+          <t>519868</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>29556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53436</t>
+          <t>52069</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63995</t>
+          <t>64515</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96566</t>
+          <t>98697</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101323</t>
+          <t>102447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140498</t>
+          <t>141502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156447</t>
+          <t>157814</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>179630</t>
+          <t>180327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>237342</t>
+          <t>235211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>269913</t>
+          <t>269393</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>403293</t>
+          <t>402289</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>442468</t>
+          <t>441344</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>164412</t>
+          <t>164340</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>217366</t>
+          <t>218178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>238111</t>
+          <t>235995</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>297241</t>
+          <t>297745</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>413344</t>
+          <t>420869</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>500464</t>
+          <t>502330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3058159</t>
+          <t>3057347</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3111113</t>
+          <t>3111185</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3081956</t>
+          <t>3081452</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3141086</t>
+          <t>3143202</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6154258</t>
+          <t>6152392</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6241378</t>
+          <t>6233853</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,97 +3712,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451155</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453105</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>880488</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>882445</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>20068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>667190</t>
+          <t>666170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>681808</t>
+          <t>681544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595934</t>
+          <t>595206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607340</t>
+          <t>607230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1267861</t>
+          <t>1267609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1286086</t>
+          <t>1286656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>36087</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>11778</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29328</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56532</t>
+          <t>57069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645185</t>
+          <t>643967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665078</t>
+          <t>664539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>676607</t>
+          <t>677204</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>693573</t>
+          <t>694157</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1329457</t>
+          <t>1328920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1354315</t>
+          <t>1355902</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36064</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63531</t>
+          <t>65465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40753</t>
+          <t>41465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71487</t>
+          <t>73987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86273</t>
+          <t>84253</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128511</t>
+          <t>127699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>551086</t>
+          <t>549152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>578553</t>
+          <t>578721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>542585</t>
+          <t>540085</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>573319</t>
+          <t>572607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1100178</t>
+          <t>1100990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1142416</t>
+          <t>1144436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67006</t>
+          <t>67317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102356</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84307</t>
+          <t>83089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122734</t>
+          <t>122246</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160278</t>
+          <t>160250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213794</t>
+          <t>211208</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325175</t>
+          <t>326070</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>360525</t>
+          <t>360214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324073</t>
+          <t>324561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>362500</t>
+          <t>363718</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>660544</t>
+          <t>663130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>714060</t>
+          <t>714088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88130</t>
+          <t>90292</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124431</t>
+          <t>124932</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>98525</t>
+          <t>97745</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133610</t>
+          <t>133183</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>199709</t>
+          <t>198186</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>251401</t>
+          <t>250441</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185355</t>
+          <t>184854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>221656</t>
+          <t>219494</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>220386</t>
+          <t>220813</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255471</t>
+          <t>256251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>412381</t>
+          <t>413341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>464073</t>
+          <t>465596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,14%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64304</t>
+          <t>63574</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95409</t>
+          <t>96569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117406</t>
+          <t>118610</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155850</t>
+          <t>156107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191124</t>
+          <t>191664</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>242013</t>
+          <t>244335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>154442</t>
+          <t>153282</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>185547</t>
+          <t>186277</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230866</t>
+          <t>230609</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>269310</t>
+          <t>268106</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>394554</t>
+          <t>392232</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>445443</t>
+          <t>444903</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>311936</t>
+          <t>315960</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>386535</t>
+          <t>387073</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,82 +6128,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>435567</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>397571</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>482700</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>787555</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>731552</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>845405</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>11,3%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>435567</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>395711</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>474950</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>787555</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>734156</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>840868</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3034646</t>
+          <t>3034108</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3109245</t>
+          <t>3105221</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,82 +6241,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>88,69%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>90,76%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3110513</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3063380</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3148509</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>87,72%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>86,39%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>5774</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6179706</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6121856</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6235709</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>88,7%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3110513</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3071130</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3150369</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>86,61%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>88,84%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>5774</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6179706</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6126393</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6233105</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>88,7%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,97 +6691,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8692</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>581545</t>
+          <t>581683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589597</t>
+          <t>589599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>559023</t>
+          <t>558531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1145348</t>
+          <t>1144417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153025</t>
+          <t>1153018</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31719</t>
+          <t>31548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37127</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637378</t>
+          <t>637549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657153</t>
+          <t>656986</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>650011</t>
+          <t>650304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659447</t>
+          <t>659499</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1293356</t>
+          <t>1293751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1313887</t>
+          <t>1314118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36453</t>
+          <t>36554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64427</t>
+          <t>65283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>38357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66448</t>
+          <t>65400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82395</t>
+          <t>80168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121014</t>
+          <t>119137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>581621</t>
+          <t>580765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609595</t>
+          <t>609494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582629</t>
+          <t>583677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609909</t>
+          <t>610720</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1174111</t>
+          <t>1175988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1212730</t>
+          <t>1214957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59445</t>
+          <t>59604</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93215</t>
+          <t>92326</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82743</t>
+          <t>81549</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>121131</t>
+          <t>120589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153560</t>
+          <t>151907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>202705</t>
+          <t>202086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>384703</t>
+          <t>385592</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418473</t>
+          <t>418314</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>375718</t>
+          <t>376260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>414106</t>
+          <t>415300</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>772062</t>
+          <t>772681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>821207</t>
+          <t>822860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82542</t>
+          <t>81555</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>115762</t>
+          <t>114897</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88760</t>
+          <t>88717</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123738</t>
+          <t>126019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>181795</t>
+          <t>183746</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233963</t>
+          <t>233163</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218568</t>
+          <t>219433</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251788</t>
+          <t>252775</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254024</t>
+          <t>251743</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>289002</t>
+          <t>289045</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>478129</t>
+          <t>478929</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>530297</t>
+          <t>528346</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63135</t>
+          <t>62147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87683</t>
+          <t>88488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105103</t>
+          <t>104291</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147766</t>
+          <t>145680</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177615</t>
+          <t>175317</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>228446</t>
+          <t>225281</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>169315</t>
+          <t>168510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>193863</t>
+          <t>194851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>252403</t>
+          <t>254489</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>295066</t>
+          <t>295878</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>428721</t>
+          <t>431886</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>479552</t>
+          <t>481850</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>283875</t>
+          <t>288562</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>351976</t>
+          <t>356536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>351406</t>
+          <t>348835</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>430726</t>
+          <t>426247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>655378</t>
+          <t>655952</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>761595</t>
+          <t>761295</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3042374</t>
+          <t>3037814</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3110475</t>
+          <t>3105788</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3113816</t>
+          <t>3118295</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3193136</t>
+          <t>3195707</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6177297</t>
+          <t>6177597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6283514</t>
+          <t>6282940</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,97 +9670,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2707</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9447</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2707</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9689</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10981</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9960</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303511</t>
+          <t>303753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703227</t>
+          <t>702206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417138</t>
+          <t>418196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500552</t>
+          <t>501996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510450</t>
+          <t>510422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>922724</t>
+          <t>922957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932919</t>
+          <t>932987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26844</t>
+          <t>27371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>13587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>32297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509494</t>
+          <t>508967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526319</t>
+          <t>526651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532914</t>
+          <t>533090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539930</t>
+          <t>539942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1047317</t>
+          <t>1046509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1064859</t>
+          <t>1065219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27469</t>
+          <t>25013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92240</t>
+          <t>93353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31213</t>
+          <t>29758</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51742</t>
+          <t>50838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54232</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129193</t>
+          <t>132568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>795546</t>
+          <t>794433</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>860317</t>
+          <t>862773</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>661139</t>
+          <t>662043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681668</t>
+          <t>683123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1471474</t>
+          <t>1468099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1546435</t>
+          <t>1537599</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96552</t>
+          <t>97471</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130347</t>
+          <t>132664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>99108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>127452</t>
+          <t>126212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>202908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247225</t>
+          <t>249620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429890</t>
+          <t>427573</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>463685</t>
+          <t>462766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417435</t>
+          <t>418675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445222</t>
+          <t>445779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>857899</t>
+          <t>855504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>903720</t>
+          <t>902216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88765</t>
+          <t>89274</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116721</t>
+          <t>116980</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191651</t>
+          <t>189705</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>493851</t>
+          <t>482778</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>288706</t>
+          <t>289958</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>683190</t>
+          <t>694020</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251444</t>
+          <t>251185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279400</t>
+          <t>278891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114517</t>
+          <t>125590</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>416717</t>
+          <t>418663</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>293343</t>
+          <t>282513</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>687827</t>
+          <t>686575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88854</t>
+          <t>87486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114071</t>
+          <t>113936</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163557</t>
+          <t>164432</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>192429</t>
+          <t>192120</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>258567</t>
+          <t>260360</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>298565</t>
+          <t>297150</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168688</t>
+          <t>168823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>193905</t>
+          <t>195273</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232296</t>
+          <t>232605</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>261168</t>
+          <t>260293</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>408919</t>
+          <t>410334</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>448917</t>
+          <t>447124</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,2%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>310253</t>
+          <t>294988</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>443635</t>
+          <t>442832</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>491218</t>
+          <t>486816</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1258568</t>
+          <t>1202240</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>874918</t>
+          <t>867714</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1732706</t>
+          <t>1724811</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3015185</t>
+          <t>3015988</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3148567</t>
+          <t>3163832</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2399465</t>
+          <t>2455793</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3166815</t>
+          <t>3171217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5384147</t>
+          <t>5392042</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6241935</t>
+          <t>6249139</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A15-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A15-Edad-trans_orig.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>728505</t>
+          <t>729530</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>618852</t>
+          <t>619148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1351866</t>
+          <t>1352015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1359943</t>
+          <t>1359972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24030</t>
+          <t>23870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21977</t>
+          <t>22018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40405</t>
+          <t>42132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613619</t>
+          <t>613779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628750</t>
+          <t>629414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>667767</t>
+          <t>667726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682539</t>
+          <t>682974</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286989</t>
+          <t>1285262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1308232</t>
+          <t>1307876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>20059</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41105</t>
+          <t>39961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>16018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34878</t>
+          <t>35785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>41693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70345</t>
+          <t>68869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478042</t>
+          <t>479186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>498386</t>
+          <t>499088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>480764</t>
+          <t>479857</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>499070</t>
+          <t>499624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>964444</t>
+          <t>965920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>993037</t>
+          <t>993096</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41423</t>
+          <t>40079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66783</t>
+          <t>66921</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46925</t>
+          <t>46430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77002</t>
+          <t>76498</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94606</t>
+          <t>95689</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132595</t>
+          <t>136111</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319927</t>
+          <t>319789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>345287</t>
+          <t>346631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326984</t>
+          <t>327488</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357061</t>
+          <t>357556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>658101</t>
+          <t>654585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>696090</t>
+          <t>695007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40208</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64283</t>
+          <t>65148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69653</t>
+          <t>71099</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100949</t>
+          <t>101311</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115649</t>
+          <t>117505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>158390</t>
+          <t>155497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228300</t>
+          <t>227435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252375</t>
+          <t>252699</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>241985</t>
+          <t>241623</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273281</t>
+          <t>271835</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>477127</t>
+          <t>480020</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519868</t>
+          <t>518012</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29556</t>
+          <t>29699</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52069</t>
+          <t>51947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64515</t>
+          <t>65757</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98697</t>
+          <t>98257</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102447</t>
+          <t>103401</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141502</t>
+          <t>141953</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157814</t>
+          <t>157936</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>180327</t>
+          <t>180184</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>235211</t>
+          <t>235651</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>269393</t>
+          <t>268151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>402289</t>
+          <t>401838</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>441344</t>
+          <t>440390</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,99%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>164340</t>
+          <t>164565</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>218178</t>
+          <t>216536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>235995</t>
+          <t>236389</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>297745</t>
+          <t>297601</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>420869</t>
+          <t>419808</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>502330</t>
+          <t>496259</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3057347</t>
+          <t>3058989</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3111185</t>
+          <t>3110960</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3081452</t>
+          <t>3081596</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3143202</t>
+          <t>3142808</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6152392</t>
+          <t>6158463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6233853</t>
+          <t>6234914</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20068</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,82 +4070,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5836</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12838</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>16292</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>8804</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>28163</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5836</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14008</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>16292</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>8795</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>27842</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>666170</t>
+          <t>666188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>681544</t>
+          <t>681627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595206</t>
+          <t>596376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607230</t>
+          <t>607253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1267609</t>
+          <t>1267288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1286656</t>
+          <t>1286647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36087</t>
+          <t>34439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28731</t>
+          <t>29695</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30087</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>56788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643967</t>
+          <t>645615</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664539</t>
+          <t>664869</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>677204</t>
+          <t>676240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>694157</t>
+          <t>693690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1328920</t>
+          <t>1329201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1355902</t>
+          <t>1355623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35896</t>
+          <t>37352</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65465</t>
+          <t>65090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41465</t>
+          <t>42106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73987</t>
+          <t>73319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84253</t>
+          <t>85744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127699</t>
+          <t>129313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>549152</t>
+          <t>549527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>578721</t>
+          <t>577265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>540085</t>
+          <t>540753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>572607</t>
+          <t>571966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1100990</t>
+          <t>1099376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1144436</t>
+          <t>1142945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67317</t>
+          <t>66839</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83089</t>
+          <t>83372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122246</t>
+          <t>119338</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160250</t>
+          <t>159962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211208</t>
+          <t>209499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326070</t>
+          <t>325849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>360214</t>
+          <t>360692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324561</t>
+          <t>327469</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>363718</t>
+          <t>363435</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>663130</t>
+          <t>664839</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>714088</t>
+          <t>714376</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90292</t>
+          <t>90398</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124932</t>
+          <t>125471</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>97745</t>
+          <t>97589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133183</t>
+          <t>133573</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>198186</t>
+          <t>196679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>250441</t>
+          <t>247818</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184854</t>
+          <t>184315</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219494</t>
+          <t>219388</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>220813</t>
+          <t>220423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256251</t>
+          <t>256407</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>413341</t>
+          <t>415964</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>465596</t>
+          <t>467103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,37%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63574</t>
+          <t>63742</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96569</t>
+          <t>94221</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118610</t>
+          <t>117462</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156107</t>
+          <t>156701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191664</t>
+          <t>192821</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>244335</t>
+          <t>240963</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>153282</t>
+          <t>155630</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>186277</t>
+          <t>186109</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230609</t>
+          <t>230015</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>268106</t>
+          <t>269254</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>392232</t>
+          <t>395604</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>444903</t>
+          <t>443746</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,71%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>315960</t>
+          <t>318298</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>387073</t>
+          <t>393069</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>397571</t>
+          <t>397636</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>482700</t>
+          <t>475543</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>731552</t>
+          <t>738161</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>845405</t>
+          <t>841006</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3034108</t>
+          <t>3028112</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3105221</t>
+          <t>3102883</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3063380</t>
+          <t>3070537</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3148509</t>
+          <t>3148444</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6121856</t>
+          <t>6126255</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6235709</t>
+          <t>6229100</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>581683</t>
+          <t>582467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589599</t>
+          <t>589597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558531</t>
+          <t>558999</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1144417</t>
+          <t>1144291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153018</t>
+          <t>1153022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31548</t>
+          <t>30308</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637549</t>
+          <t>638789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656986</t>
+          <t>656906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>650304</t>
+          <t>650669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659499</t>
+          <t>658954</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1293751</t>
+          <t>1293948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1314118</t>
+          <t>1314068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36554</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65283</t>
+          <t>64513</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38357</t>
+          <t>38551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65400</t>
+          <t>65362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80168</t>
+          <t>82739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119137</t>
+          <t>120881</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>580765</t>
+          <t>581535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609494</t>
+          <t>609459</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>583677</t>
+          <t>583715</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610720</t>
+          <t>610526</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1175988</t>
+          <t>1174244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1214957</t>
+          <t>1212386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59604</t>
+          <t>60125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92326</t>
+          <t>93871</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81549</t>
+          <t>83502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120589</t>
+          <t>119362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151907</t>
+          <t>149857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>202086</t>
+          <t>199545</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>385592</t>
+          <t>384047</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418314</t>
+          <t>417793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>376260</t>
+          <t>377487</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>415300</t>
+          <t>413347</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>772681</t>
+          <t>775222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>822860</t>
+          <t>824910</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81555</t>
+          <t>82272</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>114897</t>
+          <t>115242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88717</t>
+          <t>88452</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>126019</t>
+          <t>125354</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>183746</t>
+          <t>182732</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233163</t>
+          <t>229713</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219433</t>
+          <t>219088</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252775</t>
+          <t>252058</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251743</t>
+          <t>252408</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>289045</t>
+          <t>289310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>478929</t>
+          <t>482379</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>528346</t>
+          <t>529360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62147</t>
+          <t>62414</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88488</t>
+          <t>87825</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104291</t>
+          <t>104012</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>145680</t>
+          <t>145341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>175317</t>
+          <t>176822</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>225281</t>
+          <t>222604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168510</t>
+          <t>169173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194851</t>
+          <t>194584</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>254489</t>
+          <t>254828</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>295878</t>
+          <t>296157</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>431886</t>
+          <t>434563</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>481850</t>
+          <t>480345</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,09%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>288562</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>356536</t>
+          <t>351265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>348835</t>
+          <t>355114</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>426247</t>
+          <t>430273</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>655952</t>
+          <t>657075</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>761295</t>
+          <t>762250</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3037814</t>
+          <t>3043085</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3105788</t>
+          <t>3110609</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3118295</t>
+          <t>3114269</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3195707</t>
+          <t>3189428</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6177597</t>
+          <t>6176642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6282940</t>
+          <t>6281817</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>310493</t>
+          <t>359375</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303753</t>
+          <t>350280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>710480</t>
+          <t>767168</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>702206</t>
+          <t>757878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>13697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>422279</t>
+          <t>475525</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418196</t>
+          <t>469454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>507276</t>
+          <t>496850</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501996</t>
+          <t>491260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510422</t>
+          <t>500062</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>929555</t>
+          <t>972375</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>922957</t>
+          <t>964276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932987</t>
+          <t>975980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,27 +10351,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27371</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -10464,22 +10464,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>519624</t>
+          <t>600574</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508967</t>
+          <t>589177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526651</t>
+          <t>607925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>537551</t>
+          <t>614051</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>533090</t>
+          <t>607720</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539942</t>
+          <t>617703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1057175</t>
+          <t>1214625</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1046509</t>
+          <t>1202360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1065219</t>
+          <t>1224169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61551</t>
+          <t>63686</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25013</t>
+          <t>49966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93353</t>
+          <t>82949</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>43363</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29758</t>
+          <t>34104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50838</t>
+          <t>53789</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>102072</t>
+          <t>107049</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>90268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132568</t>
+          <t>128899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>826235</t>
+          <t>636931</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>794433</t>
+          <t>617668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>862773</t>
+          <t>650651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>672359</t>
+          <t>693523</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>662043</t>
+          <t>683097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>683123</t>
+          <t>702782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1498595</t>
+          <t>1330455</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1468099</t>
+          <t>1308605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1537599</t>
+          <t>1347236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>112954</t>
+          <t>116920</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97471</t>
+          <t>97946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132664</t>
+          <t>136471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>112339</t>
+          <t>124622</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99108</t>
+          <t>111100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126212</t>
+          <t>143185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>225293</t>
+          <t>241542</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202908</t>
+          <t>219709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249620</t>
+          <t>266539</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>447283</t>
+          <t>491439</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427573</t>
+          <t>471888</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462766</t>
+          <t>510413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>432548</t>
+          <t>482826</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>418675</t>
+          <t>464263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445779</t>
+          <t>496348</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>879831</t>
+          <t>974265</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>855504</t>
+          <t>949268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>902216</t>
+          <t>996098</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>103026</t>
+          <t>111454</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89274</t>
+          <t>96697</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116980</t>
+          <t>126989</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>335912</t>
+          <t>143186</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>189705</t>
+          <t>129453</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>482778</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>438938</t>
+          <t>254640</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>289958</t>
+          <t>234049</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>694020</t>
+          <t>276413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>265139</t>
+          <t>295626</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251185</t>
+          <t>280091</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278891</t>
+          <t>310383</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>272456</t>
+          <t>295980</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125590</t>
+          <t>281559</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>418663</t>
+          <t>309713</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>537595</t>
+          <t>591606</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>282513</t>
+          <t>569833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>686575</t>
+          <t>612197</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>72,34%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>100424</t>
+          <t>109806</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87486</t>
+          <t>96078</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113936</t>
+          <t>125008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>177784</t>
+          <t>191701</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164432</t>
+          <t>177301</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>192120</t>
+          <t>207115</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>278208</t>
+          <t>301507</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>260360</t>
+          <t>281781</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>297150</t>
+          <t>321186</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,52%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>182335</t>
+          <t>200392</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168823</t>
+          <t>185190</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>195273</t>
+          <t>214120</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>246941</t>
+          <t>271709</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232605</t>
+          <t>256295</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>260293</t>
+          <t>286109</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>429276</t>
+          <t>472101</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>410334</t>
+          <t>452422</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>447124</t>
+          <t>491827</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>395938</t>
+          <t>423495</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>294988</t>
+          <t>390015</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>442832</t>
+          <t>458262</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>678408</t>
+          <t>518329</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>486816</t>
+          <t>486233</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1202240</t>
+          <t>551151</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1074346</t>
+          <t>941824</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>867714</t>
+          <t>891729</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1724811</t>
+          <t>993896</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3062882</t>
+          <t>3108280</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3015988</t>
+          <t>3073513</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3163832</t>
+          <t>3141760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2979625</t>
+          <t>3214316</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2455793</t>
+          <t>3181494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3171217</t>
+          <t>3246412</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6042507</t>
+          <t>6322595</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5392042</t>
+          <t>6270523</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6249139</t>
+          <t>6372690</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
